--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R87ba2fcf71564d91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5066af2115b64d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R8673827a358b4ea3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R607d353244394d8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rad4c9ef03f4a4a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rebdbc218ba464e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R442b7e4dfd3e4de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re4f1b59724da4c85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re0c6c09a84094da3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R4c8f5a72e58b45c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R2b230ce175c842a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R50041db60ddf4f3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R561bb4bd412d4072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rc3182daa0881488f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R6e9f3342cd094009"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R02d0763f313c42d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R39573526c937425f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R4b26ae6662534a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R3894bad1a7744e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcbd7a5d1217943c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R1fda79d4e2964704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R3e31e3a5047249fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rd9e170709c074cb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rb13616c3e34647d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1ae998f5d4584111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R7ea63ac426a44efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R9be96b19fa264d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R3a205d7aa7e64b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ra968ea645c754e0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc94e217e9f7e4201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rf626d543998b4eb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R3a2b60cc09b243c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R96bf79cabf7d4f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3343561d6866437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rf888bdd4872d4a6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rfced049be7d74314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R7d50d70df9f340ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R913daa967d974fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R47160e1a4a1d4eea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re20b986595154a97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R88ba52a227044a4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R683090cd5187464b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8978315b3f2b43d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R7964432861144fd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R0b0ced635f7b4e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2753c7f49ba5403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R5a9efc20b1284a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R58b0449e9098418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Racf8875e3370458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R97c71b1b4b764eb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R02023651b10b43b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rcbf9ee017ae9461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb2027a6110584807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rb39c530df85a435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rf3e2b590ec424595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rf5ff1d1af10b40c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2285,11 +2285,11 @@
       </x:c>
       <x:c r="C10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Défini")</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Prototype")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Intégré")</x:f>
@@ -3678,11 +3678,11 @@
       </x:c>
       <x:c r="C37" s="41" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D37" s="41" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E37" s="41" t="n">
         <x:f>SUM(E10:E35)</x:f>
@@ -4201,7 +4201,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c6a041aa26c4c53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b7109585e194412"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4749,7 +4749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21fbb69e4e1c4a84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c5a80d0f07a488e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5297,7 +5297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R371981caaf1f43df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6baa583b7ba146ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5845,7 +5845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72e7eed74f804d64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef094c4b828406e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6393,7 +6393,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2534ee07cf24d96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radf0f8fdb2804b06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6929,7 +6929,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69536b9d48aa4228"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra45f6e14cb8646d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7210,7 +7210,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86dbe53824734ab8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3baa67b2cd7b47a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7491,7 +7491,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9eba77ec7954294"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59e161686ea94c63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7772,7 +7772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Read896cbac5b4525"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346be3b2a7694e6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8108,7 +8108,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0433d7c6f4194548"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34735bd250ab4428"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8135,7 +8135,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="102" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="77" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -8314,7 +8314,7 @@
         <x:v>Liara T’Soni</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -8341,7 +8341,7 @@
         <x:v>Interprétation originale; sous-titres attribués au locuteur et aucune reprise des voix du jeu.</x:v>
       </x:c>
       <x:c r="L7" s="9" t="str">
-        <x:v>Livrable proposé : spécification RED/characters/act-liara; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Prototype Chroniques : src/universe-actors.js, src/chronicles.js. Identifiant runtime RED-ACT-LIARA ; contexte d’œuvre/segment et sélection de scène obligatoires.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver l’absence active de Shepard, la relation Liara/Feron et le raccord vers ME2; les méthodes d’enquête ne changent pas le sort publié des protagonistes.</x:v>
@@ -8360,7 +8360,7 @@
         <x:v>https://www.penguinrandomhouse.com/books/241684/mass-effect-volume-1-redemption-by-mac-walters-various-artists/</x:v>
       </x:c>
       <x:c r="S7" s="20" t="str">
-        <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
+        <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
@@ -8371,7 +8371,7 @@
         <x:v>Feron</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -8398,7 +8398,7 @@
         <x:v>Interprétation originale; sous-titres attribués au locuteur et aucune reprise des voix du jeu.</x:v>
       </x:c>
       <x:c r="L8" s="7" t="str">
-        <x:v>Livrable proposé : spécification RED/characters/act-feron; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Prototype Chroniques : src/universe-actors.js, src/chronicles.js. Identifiant runtime RED-ACT-FERON ; contexte d’œuvre/segment et sélection de scène obligatoires.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Préserver l’absence active de Shepard, la relation Liara/Feron et le raccord vers ME2; les méthodes d’enquête ne changent pas le sort publié des protagonistes.</x:v>
@@ -8417,7 +8417,7 @@
         <x:v>https://digital.darkhorse.com/books/7bcdbde713b746338287bb0d74350bac/mass-effect-the-complete-comics</x:v>
       </x:c>
       <x:c r="S8" s="21" t="str">
-        <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
+        <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
@@ -8509,7 +8509,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2adf4888143c4b7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4259cc7bd4a84907"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9057,7 +9057,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80cb1093f364717"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3813dca00e7342a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9644,7 +9644,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R806996ec0c78491a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5870842bdfa247cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10217,7 +10217,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f7f8c8492614305"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1beb7bf0c66c45dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10753,7 +10753,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb81f3afe5ec4199"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c6ea54792894690"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11142,7 +11142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64b95bb56851482f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c7f80e6e8cc47b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11560,7 +11560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f92ec4b6558465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ffd7fc03944dbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12207,7 +12207,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R156964386f04468c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0d921004d3d4aef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12527,7 +12527,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11977d3bda924e4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref70db8d34e645b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12639,12 +12639,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="96" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Catalogue de production pour une adaptation centrée sur Liara et Feron. Les faits courts sourcés servent d’ancrages aux propositions originales de recherche, infiltration, entraide ATB et mise en scène.</x:v>
+        <x:v>Catalogue de production pour une adaptation centrée sur Liara et Feron. Les faits courts sourcés servent d’ancrages aux propositions originales de recherche, infiltration, entraide ATB et mise en scène. Prototype partiel : 2 profils sélectionnables et 0 équipements en Chroniques ; le reste demeure documentaire.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -12663,7 +12663,7 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
@@ -13421,10 +13421,16 @@
       <x:c r="E65" s="2"/>
       <x:c r="F65" s="2"/>
     </x:row>
-    <x:row r="66" ht="22" customHeight="1">
-      <x:c r="A66" s="2"/>
-      <x:c r="B66" s="2"/>
-      <x:c r="C66" s="2"/>
+    <x:row r="66" ht="96" customHeight="1">
+      <x:c r="A66" s="6" t="str">
+        <x:v>Prototype Chroniques indépendant</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="str">
+        <x:v>2 personnages sélectionnables, 0 équipements utilisables sous restrictions d’œuvre, segment, scène et porteur ; preuves dans implementationPaths et evidence des seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C66" s="6" t="str">
+        <x:v>Campagne complète, dialogues, acquisition canonique, sprites, costumes, animations et statistiques originales à réaliser ou vérifier. Les ateliers sont des essais de préparation ATB, sans progression canonique ni transfert ME1.</x:v>
+      </x:c>
       <x:c r="D66" s="2"/>
       <x:c r="E66" s="2"/>
       <x:c r="F66" s="2"/>
@@ -13980,6 +13986,14 @@
       <x:c r="D135" s="2"/>
       <x:c r="E135" s="2"/>
       <x:c r="F135" s="2"/>
+    </x:row>
+    <x:row r="136" ht="22" customHeight="1">
+      <x:c r="A136" s="2"/>
+      <x:c r="B136" s="2"/>
+      <x:c r="C136" s="2"/>
+      <x:c r="D136" s="2"/>
+      <x:c r="E136" s="2"/>
+      <x:c r="F136" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14439,7 +14453,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b06929b7e0441ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1e09ae5a6054121"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15159,7 +15173,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb62b30b0c7040e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a175d9b68c94e03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15542,7 +15556,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde5b8892e80f4486"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e3dcbaaf1bc40d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15925,7 +15939,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c5faa4deda40ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf57c1e559d84471"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16302,7 +16316,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R571612844348478a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaa7490fc681444d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16679,7 +16693,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R273061dd80154ea5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16ac2d07a20647cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17227,7 +17241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ae512b3029d48bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcaf8d7a311f4f9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ra968ea645c754e0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc94e217e9f7e4201"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rf626d543998b4eb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R3a2b60cc09b243c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R96bf79cabf7d4f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3343561d6866437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rf888bdd4872d4a6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rfced049be7d74314"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R7d50d70df9f340ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R913daa967d974fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R47160e1a4a1d4eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re20b986595154a97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R88ba52a227044a4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R683090cd5187464b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8978315b3f2b43d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R7964432861144fd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R0b0ced635f7b4e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2753c7f49ba5403e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R5a9efc20b1284a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R58b0449e9098418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Racf8875e3370458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R97c71b1b4b764eb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R02023651b10b43b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rcbf9ee017ae9461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb2027a6110584807"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rb39c530df85a435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rf3e2b590ec424595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rf5ff1d1af10b40c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R18ef1d2f1c6f4307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5b3b96ced3874199"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd58de68d497c422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R8f85d870ebaf4ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R7566e80b7b49453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rf27579680ca3457a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rbedc8cb2a3034c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rf13d24b8e5934158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rb89939687dc54c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R64d04ee23b7e4456"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rf1d06a5fb8f74c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Ra998cc47639a4aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rb10db7c7d7d54e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R7a2f961514d44caa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Re292bb797c9b4662"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R46c7945ea5214d62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R32179d30ee8c494d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rdab48b194cd84fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R12930c825bd54cd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R17b319f58f8b4dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R68e1e73bb1994189"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rd293c353e0af49c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfa888ab757014899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Racae97c7a85941f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9b6d46365cde49ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R716e64fa46d44b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rfd35e99f36e14279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R20481f2fae184c5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>117</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>8</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>94</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Défini")</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$16,"P0")</x:f>
         <x:v>4</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Défini")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$12,"P0")</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$15,"P0")</x:f>
         <x:v>9</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>117</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>94</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>19</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4048,10 +4042,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RED-S-FERON</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Feron</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4105,10 +4099,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RED-S-STORYII</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_II</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4162,10 +4156,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RED-S-FERON</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Feron</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4201,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b7109585e194412"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdf353ddd8ba4e7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4341,61 +4335,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4449,8 +4443,8 @@
         <x:v>Conception originale rattachée à Redemption #1–4, premier contact; pagination à contrôler</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4502,8 +4496,8 @@
         <x:v>Conception originale rattachée à Redemption, recherche sur Omega</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4555,8 +4549,8 @@
         <x:v>Conception originale rattachée à Redemption, transfert sur Omega; numéro à contrôler</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4608,8 +4602,8 @@
         <x:v>Conception originale rattachée à Redemption #3</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4661,8 +4655,8 @@
         <x:v>Conception originale rattachée à Redemption #3</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4714,8 +4708,8 @@
         <x:v>Conception originale rattachée à Redemption #4</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -4749,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c5a80d0f07a488e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca0f09e020954058"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4889,61 +4883,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4997,8 +4991,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5050,8 +5044,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5103,8 +5097,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5156,8 +5150,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5209,8 +5203,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5262,8 +5256,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -5297,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6baa583b7ba146ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78ef59578e7b4f43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5437,61 +5431,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5545,8 +5539,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5598,8 +5592,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5651,8 +5645,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5704,8 +5698,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5757,8 +5751,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5810,8 +5804,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -5845,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef094c4b828406e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb34a3644b6a2454a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5985,61 +5979,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6093,8 +6087,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6146,8 +6140,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6199,8 +6193,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6252,8 +6246,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6305,8 +6299,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6358,8 +6352,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -6393,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radf0f8fdb2804b06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292544c993bf43dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6533,61 +6527,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6639,8 +6633,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6690,8 +6684,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6741,8 +6735,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6792,8 +6786,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6843,8 +6837,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6894,8 +6888,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -6929,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra45f6e14cb8646d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd70bfa81c0174eb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7069,61 +7063,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7175,8 +7169,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7210,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3baa67b2cd7b47a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b683e733a0a4277"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7350,61 +7344,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7456,8 +7450,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7491,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59e161686ea94c63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a0b195e9aad48f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7631,61 +7625,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7737,8 +7731,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7772,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346be3b2a7694e6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e4c4fca7ac04e7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7912,61 +7906,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8020,8 +8014,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8073,8 +8067,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -8108,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34735bd250ab4428"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46241a045e14ab9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8248,61 +8242,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8356,10 +8350,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RED-S-BOOK</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241684/mass-effect-volume-1-redemption-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
@@ -8413,10 +8407,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RED-S-COMPLETE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://digital.darkhorse.com/books/7bcdbde713b746338287bb0d74350bac/mass-effect-the-complete-comics</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
@@ -8470,10 +8464,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RED-S-TAZZIK</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Tazzik</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -8509,7 +8503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4259cc7bd4a84907"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52783b3adab44f83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8649,61 +8643,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8757,8 +8751,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8810,8 +8804,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8863,8 +8857,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8916,8 +8910,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8969,8 +8963,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9022,8 +9016,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -9057,7 +9051,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3813dca00e7342a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rceeea5ef9a52462c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9197,61 +9191,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9303,8 +9297,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9354,8 +9348,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9405,8 +9399,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9456,8 +9450,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9507,8 +9501,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9558,8 +9552,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -9609,8 +9603,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -9644,7 +9638,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5870842bdfa247cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dbc1049cc4e431e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9784,61 +9778,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9888,8 +9882,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9937,8 +9931,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9986,8 +9980,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10035,8 +10029,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10084,8 +10078,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10133,8 +10127,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10182,8 +10176,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -10217,7 +10211,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1beb7bf0c66c45dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e44a5eee74947ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10357,61 +10351,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10463,8 +10457,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10514,8 +10508,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10565,8 +10559,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10616,8 +10610,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10667,8 +10661,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10718,8 +10712,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -10753,7 +10747,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c6ea54792894690"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a6729dd210c4cef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10893,61 +10887,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11001,8 +10995,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11054,8 +11048,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11107,8 +11101,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -11142,7 +11136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c7f80e6e8cc47b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39dabce60081418a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11282,61 +11276,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11384,8 +11378,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11431,8 +11425,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11478,8 +11472,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11525,8 +11519,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11560,7 +11554,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ffd7fc03944dbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R388f3183f015404e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11700,61 +11694,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11802,8 +11796,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11849,8 +11843,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11896,8 +11890,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11943,8 +11937,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11990,8 +11984,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12037,8 +12031,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12082,8 +12076,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12127,8 +12121,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -12172,8 +12166,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -12207,7 +12201,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0d921004d3d4aef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fa7f3bab1b4d2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12347,61 +12341,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12447,8 +12441,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12492,8 +12486,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -12527,7 +12521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref70db8d34e645b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R480a302e710e4ba4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12592,10 +12586,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -12639,12 +12633,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="96" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Catalogue de production pour une adaptation centrée sur Liara et Feron. Les faits courts sourcés servent d’ancrages aux propositions originales de recherche, infiltration, entraide ATB et mise en scène. Prototype partiel : 2 profils sélectionnables et 0 équipements en Chroniques ; le reste demeure documentaire.</x:v>
+        <x:v>117 fiches de production ; 8 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -12667,7 +12661,7 @@
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -12820,22 +12814,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -13044,13 +13038,13 @@
       <x:c r="F38" s="2"/>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
-      <x:c r="A39" s="30" t="str">
+      <x:c r="A39" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="str">
+      <x:c r="B39" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C39" s="32" t="str">
+      <x:c r="C39" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D39" s="2"/>
@@ -13435,10 +13429,16 @@
       <x:c r="E66" s="2"/>
       <x:c r="F66" s="2"/>
     </x:row>
-    <x:row r="67" ht="22" customHeight="1">
-      <x:c r="A67" s="2"/>
-      <x:c r="B67" s="2"/>
-      <x:c r="C67" s="2"/>
+    <x:row r="67" ht="96" customHeight="1">
+      <x:c r="A67" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 6 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C67" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D67" s="2"/>
       <x:c r="E67" s="2"/>
       <x:c r="F67" s="2"/>
@@ -13994,6 +13994,14 @@
       <x:c r="D136" s="2"/>
       <x:c r="E136" s="2"/>
       <x:c r="F136" s="2"/>
+    </x:row>
+    <x:row r="137" ht="22" customHeight="1">
+      <x:c r="A137" s="2"/>
+      <x:c r="B137" s="2"/>
+      <x:c r="C137" s="2"/>
+      <x:c r="D137" s="2"/>
+      <x:c r="E137" s="2"/>
+      <x:c r="F137" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14135,61 +14143,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14243,10 +14251,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RED-S-AUTHOR1</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption1/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -14300,10 +14308,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RED-S-FERON</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Feron</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -14357,10 +14365,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RED-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption2/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -14414,10 +14422,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>RED-S-COMPLETE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://digital.darkhorse.com/books/7bcdbde713b746338287bb0d74350bac/mass-effect-the-complete-comics</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -14453,7 +14461,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1e09ae5a6054121"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R205fdcff6bc24873"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14480,7 +14488,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="102" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -14593,61 +14601,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14693,10 +14701,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RED-S-BOOK</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241684/mass-effect-volume-1-redemption-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -14742,14 +14750,14 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RED-S-AUTHOR1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption1/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="54" customHeight="1">
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>RED-REF-FERON</x:v>
       </x:c>
@@ -14757,7 +14765,7 @@
         <x:v>Duo de recherche</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -14776,7 +14784,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>Livrable proposé : spécification RED/lore/ref-feron; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire RED-REF-FERON consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>Vérifier toute précision non contenue dans cette notice avant de la déclarer canon.</x:v>
@@ -14791,11 +14799,11 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RED-S-COMPLETE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://digital.darkhorse.com/books/7bcdbde713b746338287bb0d74350bac/mass-effect-the-complete-comics</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
+      <x:c r="S9" s="9" t="str">
+        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
@@ -14840,10 +14848,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>RED-S-BOOK</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241684/mass-effect-volume-1-redemption-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -14889,10 +14897,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>RED-S-FERON</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Feron</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -14938,10 +14946,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>RED-S-FERON</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Feron</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -14987,14 +14995,14 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>RED-S-TAZZIK</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Tazzik</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="68" customHeight="1">
+    <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
         <x:v>RED-SC-PURSUIT-REF</x:v>
       </x:c>
@@ -15002,7 +15010,7 @@
         <x:v>Rejoindre la base</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
         <x:v>Établi</x:v>
@@ -15021,7 +15029,7 @@
       <x:c r="J14" s="7" t="str"/>
       <x:c r="K14" s="7" t="str"/>
       <x:c r="L14" s="7" t="str">
-        <x:v>Livrable proposé : spécification RED/lore/sc-pursuit-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire RED-SC-PURSUIT-REF consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M14" s="7" t="str">
         <x:v>Préserver l’absence active de Shepard, la relation Liara/Feron et le raccord vers ME2; les méthodes d’enquête ne changent pas le sort publié des protagonistes.</x:v>
@@ -15036,14 +15044,14 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>RED-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption3/</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="68" customHeight="1">
+      <x:c r="S14" s="7" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
         <x:v>RED-SC-ACCESS-REF</x:v>
       </x:c>
@@ -15051,7 +15059,7 @@
         <x:v>Identité et accès compartimentés</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D15" s="16" t="str">
         <x:v>Établi</x:v>
@@ -15070,7 +15078,7 @@
       <x:c r="J15" s="9" t="str"/>
       <x:c r="K15" s="9" t="str"/>
       <x:c r="L15" s="9" t="str">
-        <x:v>Livrable proposé : spécification RED/lore/sc-access-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire RED-SC-ACCESS-REF consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:v>Préserver l’absence active de Shepard, la relation Liara/Feron et le raccord vers ME2; les méthodes d’enquête ne changent pas le sort publié des protagonistes.</x:v>
@@ -15085,14 +15093,14 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>RED-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption3/</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="68" customHeight="1">
+      <x:c r="S15" s="9" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
         <x:v>RED-SC-RECOVER-REF</x:v>
       </x:c>
@@ -15100,7 +15108,7 @@
         <x:v>Récupération et séparation</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
         <x:v>Établi</x:v>
@@ -15119,7 +15127,7 @@
       <x:c r="J16" s="7" t="str"/>
       <x:c r="K16" s="7" t="str"/>
       <x:c r="L16" s="7" t="str">
-        <x:v>Livrable proposé : spécification RED/lore/sc-recover-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire RED-SC-RECOVER-REF consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M16" s="7" t="str">
         <x:v>Préserver l’absence active de Shepard, la relation Liara/Feron et le raccord vers ME2; les méthodes d’enquête ne changent pas le sort publié des protagonistes.</x:v>
@@ -15134,11 +15142,11 @@
       <x:c r="Q16" s="7" t="str">
         <x:v>RED-S-AUTHOR4</x:v>
       </x:c>
-      <x:c r="R16" s="21" t="str">
+      <x:c r="R16" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption4/</x:v>
       </x:c>
-      <x:c r="S16" s="21" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
+      <x:c r="S16" s="7" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15173,7 +15181,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a175d9b68c94e03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb14e14e949224c3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15200,7 +15208,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="104" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -15313,65 +15321,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>RED-WRL-OMEGA</x:v>
       </x:c>
@@ -15379,7 +15387,7 @@
         <x:v>Omega</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -15400,7 +15408,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Livrable proposé : spécification RED/worlds/wrl-omega; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire RED-WRL-OMEGA consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver l’absence active de Shepard, la relation Liara/Feron et le raccord vers ME2; les méthodes d’enquête ne changent pas le sort publié des protagonistes.</x:v>
@@ -15415,11 +15423,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RED-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption2/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
@@ -15466,14 +15474,14 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RED-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption3/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Faraway Press écrit Alignon; Fandom écrit Alingon. Les deux graphies sont conservées ici uniquement pour contrôle.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="68" customHeight="1">
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>RED-WRL-SPACE</x:v>
       </x:c>
@@ -15481,7 +15489,7 @@
         <x:v>Poursuite dans l’espace</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -15502,7 +15510,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>Livrable proposé : spécification RED/worlds/wrl-space; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire RED-WRL-SPACE consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>Préserver l’absence active de Shepard, la relation Liara/Feron et le raccord vers ME2; les méthodes d’enquête ne changent pas le sort publié des protagonistes.</x:v>
@@ -15517,11 +15525,11 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RED-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectredemption/masseffectredemption3/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
+      <x:c r="S9" s="9" t="str">
+        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15556,7 +15564,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e3dcbaaf1bc40d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a3dc345d2f64d86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15696,61 +15704,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15802,8 +15810,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -15853,8 +15861,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -15904,8 +15912,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -15939,7 +15947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf57c1e559d84471"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85af83dc4c054aa9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16079,61 +16087,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16183,8 +16191,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16232,8 +16240,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -16281,8 +16289,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -16316,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaa7490fc681444d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0add1ba3fbea4b23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16456,61 +16464,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16560,8 +16568,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16609,8 +16617,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -16658,8 +16666,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -16693,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16ac2d07a20647cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f0cbbdd50fc4593"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16833,61 +16841,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16941,8 +16949,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16994,8 +17002,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -17047,8 +17055,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -17100,8 +17108,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -17153,8 +17161,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -17206,8 +17214,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -17241,7 +17249,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcaf8d7a311f4f9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcc327b63bb4a99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R18ef1d2f1c6f4307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5b3b96ced3874199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd58de68d497c422a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R8f85d870ebaf4ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R7566e80b7b49453e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rf27579680ca3457a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rbedc8cb2a3034c2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rf13d24b8e5934158"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rb89939687dc54c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R64d04ee23b7e4456"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rf1d06a5fb8f74c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Ra998cc47639a4aac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rb10db7c7d7d54e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R7a2f961514d44caa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Re292bb797c9b4662"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R46c7945ea5214d62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R32179d30ee8c494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rdab48b194cd84fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R12930c825bd54cd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R17b319f58f8b4dd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R68e1e73bb1994189"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rd293c353e0af49c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfa888ab757014899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Racae97c7a85941f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9b6d46365cde49ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R716e64fa46d44b1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rfd35e99f36e14279"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R20481f2fae184c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2280d4cda91245d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R63cc546340834562"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R2171e64979b64985"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rbb0e1f9cd5514bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R953ee5c929f94a94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R954e3ba39eed43a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2c4317df57934720"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R8f0b424884eb46af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R16650ed10ad645b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R549ba518e52948f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R6c98cb8dffa943e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rb9564a5f589a4784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R0b98e76d13424cd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rda7972ecc84f41b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R77a6b81ec83149a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R212f79173ca54ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R0dd86e8fc15742b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Ra23485650d4b4138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rf76a999182ea4990"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4e0c149222f34467"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R345a16dbf12a492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Re80b870acad24e9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R235da406e6684ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rf1dce1126e974d2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R17b7d08c933d4c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R52d875923bb449ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rb6b4e64b98fe4e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R4b869c586f7d4539"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdf353ddd8ba4e7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98f53423548542f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca0f09e020954058"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf32a0e6c72184d05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5291,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78ef59578e7b4f43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb7e9446ae14741"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb34a3644b6a2454a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e43de2bba34d55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6387,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292544c993bf43dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R470a628b0429468c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd70bfa81c0174eb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b5103912700492b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7204,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b683e733a0a4277"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96519f87e64d489e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7485,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a0b195e9aad48f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69c8836334984d90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7766,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e4c4fca7ac04e7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346b9dac8f854928"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8102,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46241a045e14ab9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eceab8c8cb44f55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8503,7 +8503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52783b3adab44f83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a0289e2aaa40a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9051,7 +9051,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rceeea5ef9a52462c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8185448ce6d4d01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9638,7 +9638,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dbc1049cc4e431e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cc0c2066cc54ca3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10211,7 +10211,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e44a5eee74947ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R105d7f5ebe11497f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10747,7 +10747,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a6729dd210c4cef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad44ef32dbff4b3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11136,7 +11136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39dabce60081418a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1d347930f964072"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11554,7 +11554,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R388f3183f015404e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf8f893532c140bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12201,7 +12201,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fa7f3bab1b4d2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44a789d2db1c4326"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12521,7 +12521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R480a302e710e4ba4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R396dd07a56624cef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14461,7 +14461,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R205fdcff6bc24873"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R724931d730e14888"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15181,7 +15181,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb14e14e949224c3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29781b2f91b245ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15564,7 +15564,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a3dc345d2f64d86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R244694adf9264088"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15947,7 +15947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85af83dc4c054aa9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa69f8f4606e42c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16324,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0add1ba3fbea4b23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc38f247e5cf46d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16701,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f0cbbdd50fc4593"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65bcfc7c7b824c2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17249,7 +17249,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcc327b63bb4a99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d24545b0f1a498e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2280d4cda91245d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R63cc546340834562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R2171e64979b64985"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rbb0e1f9cd5514bba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R953ee5c929f94a94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R954e3ba39eed43a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2c4317df57934720"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R8f0b424884eb46af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R16650ed10ad645b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R549ba518e52948f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R6c98cb8dffa943e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rb9564a5f589a4784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R0b98e76d13424cd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rda7972ecc84f41b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R77a6b81ec83149a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R212f79173ca54ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R0dd86e8fc15742b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Ra23485650d4b4138"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rf76a999182ea4990"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4e0c149222f34467"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R345a16dbf12a492b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Re80b870acad24e9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R235da406e6684ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rf1dce1126e974d2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R17b7d08c933d4c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R52d875923bb449ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rb6b4e64b98fe4e31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R4b869c586f7d4539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcf98a13dfa784192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R1a8afe6056984927"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rfdf0cd8905204eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R7828aab4d0004087"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R8bb83be4d98e4984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R5cde704d83db44c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rad046b8fd72c4d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R206eec92e44849b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R5120edff44374cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8762cd6797c64c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rf6bd9cb374e1456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R2c77f6d786cd4bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R2d7f80259d6f404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rc4f927ad97eb446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rb9cbd66541f84924"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rcd2d1c48e441475b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R9b216fdce7634b46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2e5f3009ca604604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Reef37bc2f4244ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R5b3406b11718426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R22b88e1b4db94941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Ra623693068794992"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rdeb0066cd5bd4134"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R9f227e7c5de848d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rd1a29a8e8852477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R46947df0d2704686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rf0cad02998964f5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R74405b7e43234d9e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98f53423548542f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49c0395a89174403"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf32a0e6c72184d05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b42a726d93a4696"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5291,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb7e9446ae14741"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Race035f4ab404b0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e43de2bba34d55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea934f6888c41dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6387,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R470a628b0429468c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc815e2aa25f4878"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b5103912700492b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3154e8617eb2474d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7204,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96519f87e64d489e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee27c7819714e96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7485,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69c8836334984d90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7519a86b0d21476b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7766,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346b9dac8f854928"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74839227dac34169"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8102,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eceab8c8cb44f55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R858b9c7131c84c5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8503,7 +8503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a0289e2aaa40a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2969d79e1a1490d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9051,7 +9051,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8185448ce6d4d01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48caa001d4154513"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9638,7 +9638,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cc0c2066cc54ca3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c6cd1b0b68344fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10211,7 +10211,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R105d7f5ebe11497f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ff59c4236c84a78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10747,7 +10747,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad44ef32dbff4b3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f7441208b043a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11136,7 +11136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1d347930f964072"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c092ffc66fb4b3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11554,7 +11554,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf8f893532c140bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R028c6768643d4f6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12201,7 +12201,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44a789d2db1c4326"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37936016b4574814"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12521,7 +12521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R396dd07a56624cef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9b3b881e1e46ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14461,7 +14461,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R724931d730e14888"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6f2dffaf15541f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15181,7 +15181,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29781b2f91b245ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72edc0c970044e14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15564,7 +15564,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R244694adf9264088"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re799a09eee394025"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15947,7 +15947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa69f8f4606e42c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bbd24b345f3421f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16324,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc38f247e5cf46d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6331c243da5b450e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16701,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65bcfc7c7b824c2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec52ca931ac453f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17249,7 +17249,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d24545b0f1a498e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc8e93811b2e4a73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Redemption_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcf98a13dfa784192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R1a8afe6056984927"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rfdf0cd8905204eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R7828aab4d0004087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R8bb83be4d98e4984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R5cde704d83db44c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rad046b8fd72c4d4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R206eec92e44849b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R5120edff44374cb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8762cd6797c64c2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rf6bd9cb374e1456f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R2c77f6d786cd4bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R2d7f80259d6f404d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rc4f927ad97eb446a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rb9cbd66541f84924"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rcd2d1c48e441475b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R9b216fdce7634b46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2e5f3009ca604604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Reef37bc2f4244ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R5b3406b11718426c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R22b88e1b4db94941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Ra623693068794992"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rdeb0066cd5bd4134"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R9f227e7c5de848d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rd1a29a8e8852477f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R46947df0d2704686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rf0cad02998964f5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R74405b7e43234d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rea2280a110f54673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2991cf02609443cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rdd5766f5bc174a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R040b85fc14c94185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rd194fb2e4ff04d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3dcd7f4fe1db4146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4ec53dde2ff34324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rce69c3ccd26446f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R9441528b68be4009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R462f7e16ee69468c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rc423ca925174427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R5edd53daf4ff4e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4dc866d829b9440a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R87ad10c6d3864b85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3da98ccd06254707"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rbfc04e3ccc9f4e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R3986685092364b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rb8d93ca4c54d4540"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R6ea7edd70fa3464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R992a0de48ea947a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rae00b3886e2840b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rf5f8e886ebb84190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Re307099c32d9400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R01f58572884f4938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rd3f444ac3dc34718"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R4d9f10585445499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R16a5a13d6f724755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2a4aafadd58b4f33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49c0395a89174403"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9219d27cdce4591"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b42a726d93a4696"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R949773530f324c80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5291,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Race035f4ab404b0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7c7df93096943dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea934f6888c41dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R952dc52bfcd74ad7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6387,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc815e2aa25f4878"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re61116518e6840c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3154e8617eb2474d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d5772822084e7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7204,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee27c7819714e96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R507929e276e74c7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7485,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7519a86b0d21476b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R455e03395b054723"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7766,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74839227dac34169"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb864ce671d3d4279"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8102,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R858b9c7131c84c5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8582e15b3e34a19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8503,7 +8503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2969d79e1a1490d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac825f2471c4e57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9051,7 +9051,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48caa001d4154513"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R747fdcdec22941c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9638,7 +9638,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c6cd1b0b68344fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7460185362cf4919"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10211,7 +10211,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ff59c4236c84a78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807aed0cb89e434c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10747,7 +10747,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f7441208b043a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e8f6c24787640f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11136,7 +11136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c092ffc66fb4b3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dc310d9f5234565"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11554,7 +11554,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R028c6768643d4f6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4575e5113fdc41c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12201,7 +12201,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37936016b4574814"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd894e06514a1481f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12521,7 +12521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9b3b881e1e46ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b37823d3f4d410f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14461,7 +14461,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6f2dffaf15541f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58de4223565247dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15181,7 +15181,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72edc0c970044e14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3592637b168f4bac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15564,7 +15564,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re799a09eee394025"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79029c53c7324dc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15947,7 +15947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bbd24b345f3421f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c1a5fa2eb07439a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16324,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6331c243da5b450e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e5f9e60a8aa4870"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16701,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec52ca931ac453f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0754a3ddbfe64b09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17249,7 +17249,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc8e93811b2e4a73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d513bd8b43d45b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>